--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13592,13 +13592,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A6F488E-841D-427F-BF76-BEB01C6A53D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B38BD9E1-3ADF-463E-9E1D-C9B9E24E3BE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BEC1DD0-26B0-4081-AF9B-003A6CED019C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{942C9AD5-6A44-4710-A96D-6E351CD65EB2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5981744-4772-476C-A1FA-0D234657D4A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26EB0DEA-9587-42D8-8638-8C6459A347F9}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13592,13 +13592,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B38BD9E1-3ADF-463E-9E1D-C9B9E24E3BE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E9B493D-DB7E-4E75-B504-32644BC7B272}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{942C9AD5-6A44-4710-A96D-6E351CD65EB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9CA6421-44CA-4397-8435-DF11ED9D1B22}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26EB0DEA-9587-42D8-8638-8C6459A347F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C051F7-B212-46F4-B721-795DE22A0833}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13592,13 +13592,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E9B493D-DB7E-4E75-B504-32644BC7B272}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAA972E3-98C7-4E70-BBF2-F26B9E405A85}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9CA6421-44CA-4397-8435-DF11ED9D1B22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0DE8453-D79F-4FAC-B704-3B65D54F45B7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2C051F7-B212-46F4-B721-795DE22A0833}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D037EA1-9F4E-4103-8204-C5D503DBF43C}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13592,13 +13592,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAA972E3-98C7-4E70-BBF2-F26B9E405A85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CBDCE87-2849-4020-8E88-DB29F6726967}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0DE8453-D79F-4FAC-B704-3B65D54F45B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11C84BFF-033C-4523-ACE5-73EED5A90519}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D037EA1-9F4E-4103-8204-C5D503DBF43C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D8FF908-8933-41F0-957F-FC5AD0EA405E}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13592,13 +13592,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CBDCE87-2849-4020-8E88-DB29F6726967}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DF71C10-22DC-40B5-9A48-C29AFCF632D9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11C84BFF-033C-4523-ACE5-73EED5A90519}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEE4B921-24E5-46D8-8679-E663B644F74A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D8FF908-8933-41F0-957F-FC5AD0EA405E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DE51416-505E-4518-A58A-0921CDEDF8D3}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13583,22 +13583,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAA972E3-98C7-4E70-BBF2-F26B9E405A85}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{22DEDDAD-CAF0-4B34-A2C0-7AF6631CE693}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0DE8453-D79F-4FAC-B704-3B65D54F45B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25935DF4-F889-4D65-A6A3-232BD3173AB0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D037EA1-9F4E-4103-8204-C5D503DBF43C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1685C97-C8C5-4F24-9862-74B810B3974D}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13583,22 +13583,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DF71C10-22DC-40B5-9A48-C29AFCF632D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D0EB0F3-0EC4-4AB7-AAC1-BF1BA3BF65DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEE4B921-24E5-46D8-8679-E663B644F74A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1911C578-3B26-4092-B8DE-540A3F22E0DC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DE51416-505E-4518-A58A-0921CDEDF8D3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{728B2B44-E23B-46B7-845A-CD62A8B6D348}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13592,13 +13592,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D0EB0F3-0EC4-4AB7-AAC1-BF1BA3BF65DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BB2FBEE-D75F-4C1D-A917-30B2AE020967}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1911C578-3B26-4092-B8DE-540A3F22E0DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13C10CE2-8110-470B-9ED4-58BF471CF441}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{728B2B44-E23B-46B7-845A-CD62A8B6D348}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C668727-D198-4D5F-86A5-75F6E91BB321}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13592,13 +13592,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BB2FBEE-D75F-4C1D-A917-30B2AE020967}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C363634-458C-49C1-B714-4015DDA1C44A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13C10CE2-8110-470B-9ED4-58BF471CF441}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8892A9AA-6A3F-4D7A-AE5F-E95FC6E2F7B5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C668727-D198-4D5F-86A5-75F6E91BB321}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6A06286-4D5A-48DB-87CF-E0442B4ABF87}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13592,13 +13592,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C363634-458C-49C1-B714-4015DDA1C44A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACFCF95F-DB01-4958-9658-9F4031087C1B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8892A9AA-6A3F-4D7A-AE5F-E95FC6E2F7B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BE0DE4B-8D25-4E71-9BA3-610E9F6C2DC4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6A06286-4D5A-48DB-87CF-E0442B4ABF87}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2331D628-6C09-4782-B394-F777428DD2C7}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q199"/>
+  <dimension ref="A1:Q200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7984,16 +7984,16 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Spalax ehrenbergi</t>
+          <t>Rattus norvegicus</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Spalax ehrenbergi</t>
+          <t>Rattus rattus</t>
         </is>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -8011,24 +8011,24 @@
         <v>0</v>
       </c>
       <c r="I118">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L118">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Other plant</t>
+          <t>Seed</t>
         </is>
       </c>
       <c r="N118">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -8049,12 +8049,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Bathyergus suillus</t>
+          <t>Spalax ehrenbergi</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Bathyergus suillus</t>
+          <t>Spalax ehrenbergi</t>
         </is>
       </c>
       <c r="C119">
@@ -8082,10 +8082,10 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L119">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M119" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         </is>
       </c>
       <c r="N119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -8114,12 +8114,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cryptomys hottentotus</t>
+          <t>Bathyergus suillus</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cryptomys hottentotus</t>
+          <t>Bathyergus suillus</t>
         </is>
       </c>
       <c r="C120">
@@ -8172,19 +8172,19 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>Cathemeral</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Fukomys mechowii</t>
+          <t>Cryptomys hottentotus</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cryptomys mechowi</t>
+          <t>Cryptomys hottentotus</t>
         </is>
       </c>
       <c r="C121">
@@ -8244,12 +8244,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Fukomys darlingi</t>
+          <t>Fukomys mechowii</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Cryptomys darlingi</t>
+          <t>Cryptomys mechowi</t>
         </is>
       </c>
       <c r="C122">
@@ -8309,12 +8309,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Fukomys damarensis</t>
+          <t>Fukomys darlingi</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cryptomys damarensis</t>
+          <t>Cryptomys darlingi</t>
         </is>
       </c>
       <c r="C123">
@@ -8374,12 +8374,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Fukomys anselli</t>
+          <t>Fukomys damarensis</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cryptomys anselli</t>
+          <t>Cryptomys damarensis</t>
         </is>
       </c>
       <c r="C124">
@@ -8439,12 +8439,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Georychus capensis</t>
+          <t>Fukomys anselli</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Georychus capensis</t>
+          <t>Cryptomys anselli</t>
         </is>
       </c>
       <c r="C125">
@@ -8497,19 +8497,19 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Diurnal</t>
+          <t>Cathemeral</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Heliophobius argenteocinereus</t>
+          <t>Georychus capensis</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Heliophobius argenteocinereus</t>
+          <t>Georychus capensis</t>
         </is>
       </c>
       <c r="C126">
@@ -8569,12 +8569,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Heterocephalus glaber</t>
+          <t>Heliophobius argenteocinereus</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Heterocephalus glaber</t>
+          <t>Heliophobius argenteocinereus</t>
         </is>
       </c>
       <c r="C127">
@@ -8627,19 +8627,19 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>Cathemeral</t>
+          <t>Diurnal</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Proechimys guyannensis</t>
+          <t>Heterocephalus glaber</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Proechimys guyannensis</t>
+          <t>Heterocephalus glaber</t>
         </is>
       </c>
       <c r="C128">
@@ -8661,16 +8661,16 @@
         <v>0</v>
       </c>
       <c r="I128">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L128">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="N128">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -8692,19 +8692,19 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Cathemeral</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cavia porcellus</t>
+          <t>Proechimys guyannensis</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cavia porcellus</t>
+          <t>Proechimys guyannensis</t>
         </is>
       </c>
       <c r="C129">
@@ -8726,16 +8726,16 @@
         <v>0</v>
       </c>
       <c r="I129">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L129">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="N129">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -8757,19 +8757,19 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>Crepuscular</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Hydrochoerus hydrochaeris</t>
+          <t>Cavia porcellus</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Hydrochoerus hydrochaeris</t>
+          <t>Cavia porcellus</t>
         </is>
       </c>
       <c r="C130">
@@ -8791,7 +8791,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -8800,7 +8800,7 @@
         <v>0</v>
       </c>
       <c r="L130">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="N130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -8822,19 +8822,19 @@
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>Diurnal</t>
+          <t>Crepuscular</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Oryctolagus cuniculus</t>
+          <t>Hydrochoerus hydrochaeris</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Oryctolagus cuniculus</t>
+          <t>Hydrochoerus hydrochaeris</t>
         </is>
       </c>
       <c r="C131">
@@ -8856,7 +8856,7 @@
         <v>0</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="L131">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="N131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -8887,41 +8887,41 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Diurnal</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Atelerix algirus</t>
+          <t>Oryctolagus cuniculus</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Atelerix algirus</t>
+          <t>Oryctolagus cuniculus</t>
         </is>
       </c>
       <c r="C132">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D132">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E132">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F132">
         <v>0</v>
       </c>
       <c r="G132">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H132">
         <v>0</v>
       </c>
       <c r="I132">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -8930,19 +8930,19 @@
         <v>0</v>
       </c>
       <c r="L132">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Ectotherm vertebrates</t>
+          <t>Other plant</t>
         </is>
       </c>
       <c r="N132">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Faunivore</t>
+          <t>Herbivore</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -8959,34 +8959,34 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Atelerix algirus</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Atelerix algirus</t>
         </is>
       </c>
       <c r="C133">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D133">
         <v>10</v>
       </c>
       <c r="E133">
+        <v>30</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133">
         <v>10</v>
       </c>
-      <c r="F133">
-        <v>0</v>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
       <c r="H133">
         <v>0</v>
       </c>
       <c r="I133">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J133">
         <v>0</v>
@@ -8995,15 +8995,15 @@
         <v>0</v>
       </c>
       <c r="L133">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Invertebrates</t>
+          <t>Ectotherm vertebrates</t>
         </is>
       </c>
       <c r="N133">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -9024,40 +9024,40 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Hemiechinus auritus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Hemiechinus auritus</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="C134">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E134">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F134">
         <v>0</v>
       </c>
       <c r="G134">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H134">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I134">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L134">
         <v>0</v>
@@ -9068,7 +9068,7 @@
         </is>
       </c>
       <c r="N134">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -9089,40 +9089,40 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Echinosorex gymnura</t>
+          <t>Hemiechinus auritus</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Echinosorex gymnura</t>
+          <t>Hemiechinus auritus</t>
         </is>
       </c>
       <c r="C135">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
         <v>30</v>
       </c>
-      <c r="F135">
+      <c r="H135">
         <v>20</v>
       </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
       <c r="I135">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J135">
         <v>0</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L135">
         <v>0</v>
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="N135">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -9154,25 +9154,25 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Hylomys suillus</t>
+          <t>Echinosorex gymnura</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Hylomys suillus</t>
+          <t>Echinosorex gymnura</t>
         </is>
       </c>
       <c r="C136">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F136">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="N136">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -9212,29 +9212,29 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Cathemeral</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Solenodon paradoxus</t>
+          <t>Hylomys suillus</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Solenodon paradoxus</t>
+          <t>Hylomys suillus</t>
         </is>
       </c>
       <c r="C137">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D137">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E137">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="I137">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -9255,7 +9255,7 @@
         <v>0</v>
       </c>
       <c r="L137">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -9263,11 +9263,11 @@
         </is>
       </c>
       <c r="N137">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Omnivore</t>
+          <t>Faunivore</t>
         </is>
       </c>
       <c r="P137" t="inlineStr">
@@ -9277,29 +9277,29 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Cathemeral</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Crocidura russula</t>
+          <t>Solenodon paradoxus</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Crocidura russula</t>
+          <t>Solenodon paradoxus</t>
         </is>
       </c>
       <c r="C138">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E138">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -9308,10 +9308,10 @@
         <v>0</v>
       </c>
       <c r="H138">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I138">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J138">
         <v>0</v>
@@ -9320,7 +9320,7 @@
         <v>0</v>
       </c>
       <c r="L138">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -9328,11 +9328,11 @@
         </is>
       </c>
       <c r="N138">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
-          <t>Faunivore</t>
+          <t>Omnivore</t>
         </is>
       </c>
       <c r="P138" t="inlineStr">
@@ -9349,12 +9349,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Crocidura flavescens</t>
+          <t>Crocidura russula</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Crocidura flavescens</t>
+          <t>Crocidura russula</t>
         </is>
       </c>
       <c r="C139">
@@ -9414,12 +9414,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Crocidura jacksoni</t>
+          <t>Crocidura flavescens</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Crocidura jacksoni</t>
+          <t>Crocidura flavescens</t>
         </is>
       </c>
       <c r="C140">
@@ -9479,12 +9479,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Crocidura hildegardeae</t>
+          <t>Crocidura jacksoni</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Crocidura hildegardeae</t>
+          <t>Crocidura jacksoni</t>
         </is>
       </c>
       <c r="C141">
@@ -9544,31 +9544,31 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Suncus megalura</t>
+          <t>Crocidura hildegardeae</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Suncus megalura</t>
+          <t>Crocidura hildegardeae</t>
         </is>
       </c>
       <c r="C142">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F142">
         <v>0</v>
       </c>
       <c r="G142">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H142">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -9609,12 +9609,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Suncus murinus</t>
+          <t>Suncus megalura</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Suncus murinus</t>
+          <t>Suncus megalura</t>
         </is>
       </c>
       <c r="C143">
@@ -9674,12 +9674,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Suncus etruscus</t>
+          <t>Suncus murinus</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Suncus etruscus</t>
+          <t>Suncus murinus</t>
         </is>
       </c>
       <c r="C144">
@@ -9739,16 +9739,16 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ruwenzorisorex suncoides</t>
+          <t>Suncus etruscus</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ruwenzorisorex suncoides</t>
+          <t>Suncus etruscus</t>
         </is>
       </c>
       <c r="C145">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -9760,10 +9760,10 @@
         <v>0</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I145">
         <v>0</v>
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="N145">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -9804,16 +9804,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sylvisorex granti</t>
+          <t>Ruwenzorisorex suncoides</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Sylvisorex granti</t>
+          <t>Ruwenzorisorex suncoides</t>
         </is>
       </c>
       <c r="C146">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -9825,10 +9825,10 @@
         <v>0</v>
       </c>
       <c r="G146">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I146">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         </is>
       </c>
       <c r="N146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -9857,28 +9857,28 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Scansorial</t>
+          <t>Ground</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>Cathemeral</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sorex minutus</t>
+          <t>Sylvisorex granti</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Sorex minutus</t>
+          <t>Sylvisorex granti</t>
         </is>
       </c>
       <c r="C147">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -9890,10 +9890,10 @@
         <v>0</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H147">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -9913,7 +9913,7 @@
         </is>
       </c>
       <c r="N147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>Scansorial</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
@@ -9934,12 +9934,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sorex araneus</t>
+          <t>Sorex minutus</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sorex araneus</t>
+          <t>Sorex minutus</t>
         </is>
       </c>
       <c r="C148">
@@ -9999,12 +9999,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sorex cinereus</t>
+          <t>Sorex araneus</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Sorex cinereus</t>
+          <t>Sorex araneus</t>
         </is>
       </c>
       <c r="C149">
@@ -10064,12 +10064,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sorex fumeus</t>
+          <t>Sorex cinereus</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sorex fumeus</t>
+          <t>Sorex cinereus</t>
         </is>
       </c>
       <c r="C150">
@@ -10129,16 +10129,16 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Blarina brevicauda</t>
+          <t>Sorex fumeus</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Blarina brevicauda</t>
+          <t>Sorex fumeus</t>
         </is>
       </c>
       <c r="C151">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -10150,11 +10150,11 @@
         <v>0</v>
       </c>
       <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
         <v>30</v>
       </c>
-      <c r="H151">
-        <v>0</v>
-      </c>
       <c r="I151">
         <v>0</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="L151">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         </is>
       </c>
       <c r="N151">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -10194,12 +10194,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Neomys fodiens</t>
+          <t>Blarina brevicauda</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Neomys fodiens</t>
+          <t>Blarina brevicauda</t>
         </is>
       </c>
       <c r="C152">
@@ -10209,28 +10209,28 @@
         <v>0</v>
       </c>
       <c r="E152">
+        <v>0</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+      <c r="G152">
         <v>30</v>
       </c>
-      <c r="F152">
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
         <v>30</v>
-      </c>
-      <c r="G152">
-        <v>0</v>
-      </c>
-      <c r="H152">
-        <v>0</v>
-      </c>
-      <c r="I152">
-        <v>0</v>
-      </c>
-      <c r="J152">
-        <v>0</v>
-      </c>
-      <c r="K152">
-        <v>0</v>
-      </c>
-      <c r="L152">
-        <v>0</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -10259,25 +10259,25 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Myosorex babaulti</t>
+          <t>Neomys fodiens</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Myosorex babaulti</t>
+          <t>Neomys fodiens</t>
         </is>
       </c>
       <c r="C153">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D153">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="N153">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -10324,25 +10324,25 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Condylura cristata</t>
+          <t>Myosorex babaulti</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Condylura cristata</t>
+          <t>Myosorex babaulti</t>
         </is>
       </c>
       <c r="C154">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E154">
         <v>0</v>
       </c>
       <c r="F154">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -10389,16 +10389,16 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Parascalops breweri</t>
+          <t>Condylura cristata</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Parascalops breweri</t>
+          <t>Condylura cristata</t>
         </is>
       </c>
       <c r="C155">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="D155">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>0</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G155">
         <v>0</v>
@@ -10433,7 +10433,7 @@
         </is>
       </c>
       <c r="N155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -10454,12 +10454,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Scalopus aquaticus</t>
+          <t>Parascalops breweri</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Scalopus aquaticus</t>
+          <t>Parascalops breweri</t>
         </is>
       </c>
       <c r="C156">
@@ -10519,25 +10519,25 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Desmana moschata</t>
+          <t>Scalopus aquaticus</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Desmana moschata</t>
+          <t>Scalopus aquaticus</t>
         </is>
       </c>
       <c r="C157">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F157">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="N157">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -10577,32 +10577,32 @@
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Cathemeral</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Galemys pyrenaicus</t>
+          <t>Desmana moschata</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Galemys pyrenaicus</t>
+          <t>Desmana moschata</t>
         </is>
       </c>
       <c r="C158">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F158">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="N158">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -10649,16 +10649,16 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Talpa europaea</t>
+          <t>Galemys pyrenaicus</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Talpa europaea</t>
+          <t>Galemys pyrenaicus</t>
         </is>
       </c>
       <c r="C159">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -10667,7 +10667,7 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G159">
         <v>0</v>
@@ -10693,7 +10693,7 @@
         </is>
       </c>
       <c r="N159">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -10707,23 +10707,23 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>Cathemeral</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Casinycteris argynnis</t>
+          <t>Talpa europaea</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Casinycteris argynnis</t>
+          <t>Talpa europaea</t>
         </is>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -10741,10 +10741,10 @@
         <v>0</v>
       </c>
       <c r="I160">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J160">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K160">
         <v>0</v>
@@ -10754,37 +10754,37 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Invertebrates</t>
         </is>
       </c>
       <c r="N160">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Herbivore</t>
+          <t>Faunivore</t>
         </is>
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Arboreal</t>
+          <t>Ground</t>
         </is>
       </c>
       <c r="Q160" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Cathemeral</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Epomophorus wahlbergi</t>
+          <t>Casinycteris argynnis</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Epomophorus wahlbergi</t>
+          <t>Casinycteris argynnis</t>
         </is>
       </c>
       <c r="C161">
@@ -10806,10 +10806,10 @@
         <v>0</v>
       </c>
       <c r="I161">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="J161">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K161">
         <v>0</v>
@@ -10823,7 +10823,7 @@
         </is>
       </c>
       <c r="N161">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -10844,12 +10844,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Epomops franqueti</t>
+          <t>Epomophorus wahlbergi</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Epomops franqueti</t>
+          <t>Epomophorus wahlbergi</t>
         </is>
       </c>
       <c r="C162">
@@ -10909,12 +10909,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Rousettus aegyptiacus</t>
+          <t>Epomops franqueti</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Rousettus aegyptiacus</t>
+          <t>Epomops franqueti</t>
         </is>
       </c>
       <c r="C163">
@@ -10936,10 +10936,10 @@
         <v>0</v>
       </c>
       <c r="I163">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J163">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K163">
         <v>0</v>
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="N163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -10974,19 +10974,19 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Hypsignathus monstrosus</t>
+          <t>Rousettus aegyptiacus</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Hypsignathus monstrosus</t>
+          <t>Rousettus aegyptiacus</t>
         </is>
       </c>
       <c r="C164">
         <v>0</v>
       </c>
       <c r="D164">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -11001,10 +11001,10 @@
         <v>0</v>
       </c>
       <c r="I164">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="J164">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K164">
         <v>0</v>
@@ -11039,19 +11039,19 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Megaloglossus woermanni</t>
+          <t>Hypsignathus monstrosus</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Megaloglossus woermanni</t>
+          <t>Hypsignathus monstrosus</t>
         </is>
       </c>
       <c r="C165">
         <v>0</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -11066,10 +11066,10 @@
         <v>0</v>
       </c>
       <c r="I165">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J165">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K165">
         <v>0</v>
@@ -11079,11 +11079,11 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Nectar</t>
+          <t>Fruit</t>
         </is>
       </c>
       <c r="N165">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -11104,12 +11104,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Scotonycteris zenkeri</t>
+          <t>Megaloglossus woermanni</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Scotonycteris zenkeri</t>
+          <t>Megaloglossus woermanni</t>
         </is>
       </c>
       <c r="C166">
@@ -11131,11 +11131,11 @@
         <v>0</v>
       </c>
       <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
         <v>100</v>
       </c>
-      <c r="J166">
-        <v>0</v>
-      </c>
       <c r="K166">
         <v>0</v>
       </c>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Nectar</t>
         </is>
       </c>
       <c r="N166">
@@ -11169,35 +11169,35 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Macronycteris commersoni</t>
+          <t>Scotonycteris zenkeri</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Hipposideros commersoni</t>
+          <t>Scotonycteris zenkeri</t>
         </is>
       </c>
       <c r="C167">
+        <v>0</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="F167">
+        <v>0</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
         <v>100</v>
       </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-      <c r="E167">
-        <v>0</v>
-      </c>
-      <c r="F167">
-        <v>0</v>
-      </c>
-      <c r="G167">
-        <v>0</v>
-      </c>
-      <c r="H167">
-        <v>0</v>
-      </c>
-      <c r="I167">
-        <v>0</v>
-      </c>
       <c r="J167">
         <v>0</v>
       </c>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Invertebrates</t>
+          <t>Fruit</t>
         </is>
       </c>
       <c r="N167">
@@ -11217,12 +11217,12 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Faunivore</t>
+          <t>Herbivore</t>
         </is>
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>Arboreal</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
@@ -11234,12 +11234,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Triaenops persicus</t>
+          <t>Macronycteris commersoni</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Triaenops persicus</t>
+          <t>Hipposideros commersoni</t>
         </is>
       </c>
       <c r="C168">
@@ -11299,12 +11299,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Cardioderma cor</t>
+          <t>Triaenops persicus</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Cardioderma cor</t>
+          <t>Triaenops persicus</t>
         </is>
       </c>
       <c r="C169">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
@@ -11364,12 +11364,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Coleura afra</t>
+          <t>Cardioderma cor</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Coleura afra</t>
+          <t>Cardioderma cor</t>
         </is>
       </c>
       <c r="C170">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>Ground</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
@@ -11429,12 +11429,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mops pumilus</t>
+          <t>Coleura afra</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Chaerephon pumilus</t>
+          <t>Coleura afra</t>
         </is>
       </c>
       <c r="C171">
@@ -11494,12 +11494,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Miniopterus schreibersii</t>
+          <t>Mops pumilus</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Miniopterus schreibersii</t>
+          <t>Chaerephon pumilus</t>
         </is>
       </c>
       <c r="C172">
@@ -11559,19 +11559,19 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Felis catus</t>
+          <t>Miniopterus schreibersii</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Felis catus</t>
+          <t>Miniopterus schreibersii</t>
         </is>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D173">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Endotherm vertebrates</t>
+          <t>Invertebrates</t>
         </is>
       </c>
       <c r="N173">
@@ -11612,31 +11612,31 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>Cathemeral</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Panthera leo</t>
+          <t>Felis catus</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Panthera leo</t>
+          <t>Felis catus</t>
         </is>
       </c>
       <c r="C174">
         <v>0</v>
       </c>
       <c r="D174">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -11648,7 +11648,7 @@
         <v>0</v>
       </c>
       <c r="H174">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I174">
         <v>0</v>
@@ -11668,7 +11668,7 @@
         </is>
       </c>
       <c r="N174">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -11682,27 +11682,27 @@
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Cathemeral</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Cynictis penicillata</t>
+          <t>Panthera leo</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Cynictis penicillata</t>
+          <t>Panthera leo</t>
         </is>
       </c>
       <c r="C175">
+        <v>0</v>
+      </c>
+      <c r="D175">
         <v>90</v>
       </c>
-      <c r="D175">
-        <v>0</v>
-      </c>
       <c r="E175">
         <v>0</v>
       </c>
@@ -11710,11 +11710,11 @@
         <v>0</v>
       </c>
       <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
         <v>10</v>
       </c>
-      <c r="H175">
-        <v>0</v>
-      </c>
       <c r="I175">
         <v>0</v>
       </c>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Invertebrates</t>
+          <t>Endotherm vertebrates</t>
         </is>
       </c>
       <c r="N175">
@@ -11747,23 +11747,23 @@
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>Diurnal</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Mungos mungo</t>
+          <t>Cynictis penicillata</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Mungos mungo</t>
+          <t>Cynictis penicillata</t>
         </is>
       </c>
       <c r="C176">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -11775,7 +11775,7 @@
         <v>0</v>
       </c>
       <c r="G176">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H176">
         <v>0</v>
@@ -11819,19 +11819,19 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Crocuta crocuta</t>
+          <t>Mungos mungo</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Crocuta crocuta</t>
+          <t>Mungos mungo</t>
         </is>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D177">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -11840,7 +11840,7 @@
         <v>0</v>
       </c>
       <c r="G177">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H177">
         <v>0</v>
@@ -11859,11 +11859,11 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Endotherm vertebrates</t>
+          <t>Invertebrates</t>
         </is>
       </c>
       <c r="N177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -11877,26 +11877,26 @@
       </c>
       <c r="Q177" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Diurnal</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Hyaena hyaena</t>
+          <t>Crocuta crocuta</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Hyaena hyaena</t>
+          <t>Crocuta crocuta</t>
         </is>
       </c>
       <c r="C178">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D178">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -11908,10 +11908,10 @@
         <v>0</v>
       </c>
       <c r="H178">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I178">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -11924,11 +11924,11 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Carrion/scavenge</t>
+          <t>Endotherm vertebrates</t>
         </is>
       </c>
       <c r="N178">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -11949,35 +11949,35 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Vulpes zerda</t>
+          <t>Hyaena hyaena</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Vulpes zerda</t>
+          <t>Hyaena hyaena</t>
         </is>
       </c>
       <c r="C179">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D179">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E179">
+        <v>0</v>
+      </c>
+      <c r="F179">
+        <v>0</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>70</v>
+      </c>
+      <c r="I179">
         <v>10</v>
       </c>
-      <c r="F179">
-        <v>0</v>
-      </c>
-      <c r="G179">
-        <v>10</v>
-      </c>
-      <c r="H179">
-        <v>0</v>
-      </c>
-      <c r="I179">
-        <v>0</v>
-      </c>
       <c r="J179">
         <v>0</v>
       </c>
@@ -11985,15 +11985,15 @@
         <v>0</v>
       </c>
       <c r="L179">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Endotherm vertebrates</t>
+          <t>Carrion/scavenge</t>
         </is>
       </c>
       <c r="N179">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -12014,51 +12014,51 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Canis latrans</t>
+          <t>Vulpes zerda</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Canis latrans</t>
+          <t>Vulpes zerda</t>
         </is>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D180">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E180">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F180">
+        <v>0</v>
+      </c>
+      <c r="G180">
         <v>10</v>
       </c>
-      <c r="G180">
-        <v>0</v>
-      </c>
       <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
         <v>30</v>
       </c>
-      <c r="I180">
-        <v>0</v>
-      </c>
-      <c r="J180">
-        <v>0</v>
-      </c>
-      <c r="K180">
-        <v>0</v>
-      </c>
-      <c r="L180">
-        <v>0</v>
-      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Endotherm vertebrates</t>
         </is>
       </c>
       <c r="N180">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -12079,31 +12079,31 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Mustela erminea</t>
+          <t>Canis latrans</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Mustela erminea</t>
+          <t>Canis latrans</t>
         </is>
       </c>
       <c r="C181">
+        <v>0</v>
+      </c>
+      <c r="D181">
+        <v>60</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
+      <c r="F181">
         <v>10</v>
       </c>
-      <c r="D181">
-        <v>70</v>
-      </c>
-      <c r="E181">
-        <v>10</v>
-      </c>
-      <c r="F181">
-        <v>0</v>
-      </c>
       <c r="G181">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H181">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I181">
         <v>0</v>
@@ -12123,7 +12123,7 @@
         </is>
       </c>
       <c r="N181">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -12144,28 +12144,28 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Mustela putorius</t>
+          <t>Mustela erminea</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Mustela putorius</t>
+          <t>Mustela erminea</t>
         </is>
       </c>
       <c r="C182">
         <v>10</v>
       </c>
       <c r="D182">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E182">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F182">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H182">
         <v>0</v>
@@ -12202,41 +12202,41 @@
       </c>
       <c r="Q182" t="inlineStr">
         <is>
-          <t>Cathemeral</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Galictis vittatus</t>
+          <t>Mustela putorius</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Galictis vittata</t>
+          <t>Mustela putorius</t>
         </is>
       </c>
       <c r="C183">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D183">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E183">
         <v>20</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G183">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H183">
         <v>0</v>
       </c>
       <c r="I183">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J183">
         <v>0</v>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="N183">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -12274,35 +12274,35 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Mustela vison</t>
+          <t>Galictis vittatus</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Neovison vison</t>
+          <t>Galictis vittata</t>
         </is>
       </c>
       <c r="C184">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D184">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E184">
         <v>20</v>
       </c>
       <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>10</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
         <v>20</v>
       </c>
-      <c r="G184">
-        <v>0</v>
-      </c>
-      <c r="H184">
-        <v>0</v>
-      </c>
-      <c r="I184">
-        <v>0</v>
-      </c>
       <c r="J184">
         <v>0</v>
       </c>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="N184">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -12332,32 +12332,32 @@
       </c>
       <c r="Q184" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Cathemeral</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Ursus arctos</t>
+          <t>Mustela vison</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Ursus arctos</t>
+          <t>Neovison vison</t>
         </is>
       </c>
       <c r="C185">
         <v>10</v>
       </c>
       <c r="D185">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G185">
         <v>0</v>
@@ -12366,7 +12366,7 @@
         <v>0</v>
       </c>
       <c r="I185">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -12375,11 +12375,11 @@
         <v>0</v>
       </c>
       <c r="L185">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Other plant</t>
+          <t>Endotherm vertebrates</t>
         </is>
       </c>
       <c r="N185">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Herbivore</t>
+          <t>Faunivore</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">
@@ -12397,32 +12397,32 @@
       </c>
       <c r="Q185" t="inlineStr">
         <is>
-          <t>Diurnal</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Ursus maritimus</t>
+          <t>Ursus arctos</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Ursus maritimus</t>
+          <t>Ursus arctos</t>
         </is>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D186">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="E186">
         <v>0</v>
       </c>
       <c r="F186">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G186">
         <v>0</v>
@@ -12431,7 +12431,7 @@
         <v>0</v>
       </c>
       <c r="I186">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -12440,19 +12440,19 @@
         <v>0</v>
       </c>
       <c r="L186">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Endotherm vertebrates</t>
+          <t>Other plant</t>
         </is>
       </c>
       <c r="N186">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Faunivore</t>
+          <t>Herbivore</t>
         </is>
       </c>
       <c r="P186" t="inlineStr">
@@ -12469,25 +12469,25 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Zalophus californianus</t>
+          <t>Ursus maritimus</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Zalophus californianus</t>
+          <t>Ursus maritimus</t>
         </is>
       </c>
       <c r="C187">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E187">
         <v>0</v>
       </c>
       <c r="F187">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G187">
         <v>0</v>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Fish</t>
+          <t>Endotherm vertebrates</t>
         </is>
       </c>
       <c r="N187">
@@ -12522,37 +12522,37 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>Ground</t>
         </is>
       </c>
       <c r="Q187" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Diurnal</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Nasua narica</t>
+          <t>Zalophus californianus</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Nasua narica</t>
+          <t>Zalophus californianus</t>
         </is>
       </c>
       <c r="C188">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D188">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E188">
         <v>0</v>
       </c>
       <c r="F188">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G188">
         <v>0</v>
@@ -12561,7 +12561,7 @@
         <v>0</v>
       </c>
       <c r="I188">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J188">
         <v>0</v>
@@ -12574,44 +12574,44 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="N188">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>Herbivore</t>
+          <t>Faunivore</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Scansorial</t>
+          <t>Marine</t>
         </is>
       </c>
       <c r="Q188" t="inlineStr">
         <is>
-          <t>Diurnal</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Potos flavus</t>
+          <t>Nasua narica</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Potos flavus</t>
+          <t>Nasua narica</t>
         </is>
       </c>
       <c r="C189">
         <v>10</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -12620,13 +12620,13 @@
         <v>0</v>
       </c>
       <c r="G189">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H189">
         <v>0</v>
       </c>
       <c r="I189">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J189">
         <v>0</v>
@@ -12652,72 +12652,72 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Arboreal</t>
+          <t>Scansorial</t>
         </is>
       </c>
       <c r="Q189" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Diurnal</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Procyon lotor</t>
+          <t>Potos flavus</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Procyon lotor</t>
+          <t>Potos flavus</t>
         </is>
       </c>
       <c r="C190">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D190">
         <v>0</v>
       </c>
       <c r="E190">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F190">
         <v>0</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H190">
         <v>0</v>
       </c>
       <c r="I190">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="J190">
         <v>0</v>
       </c>
       <c r="K190">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L190">
         <v>0</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Invertebrates</t>
+          <t>Fruit</t>
         </is>
       </c>
       <c r="N190">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Omnivore</t>
+          <t>Herbivore</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Ground</t>
+          <t>Arboreal</t>
         </is>
       </c>
       <c r="Q190" t="inlineStr">
@@ -12729,22 +12729,22 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Ailurus fulgens</t>
+          <t>Procyon lotor</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Ailurus fulgens</t>
+          <t>Procyon lotor</t>
         </is>
       </c>
       <c r="C191">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="D191">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -12756,28 +12756,28 @@
         <v>0</v>
       </c>
       <c r="I191">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J191">
         <v>0</v>
       </c>
       <c r="K191">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L191">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Other plant</t>
+          <t>Invertebrates</t>
         </is>
       </c>
       <c r="N191">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Herbivore</t>
+          <t>Omnivore</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -12787,26 +12787,26 @@
       </c>
       <c r="Q191" t="inlineStr">
         <is>
-          <t>Cathemeral</t>
+          <t>Nocturnal</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Equus burchelli</t>
+          <t>Ailurus fulgens</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Equus burchellii</t>
+          <t>Ailurus fulgens</t>
         </is>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -12821,16 +12821,16 @@
         <v>0</v>
       </c>
       <c r="I192">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J192">
         <v>0</v>
       </c>
       <c r="K192">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L192">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="N192">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Equus quagga</t>
+          <t>Equus burchellii</t>
         </is>
       </c>
       <c r="C193">
@@ -12924,12 +12924,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Lama glama</t>
+          <t>Equus burchelli</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Lama glama</t>
+          <t>Equus quagga</t>
         </is>
       </c>
       <c r="C194">
@@ -12982,19 +12982,19 @@
       </c>
       <c r="Q194" t="inlineStr">
         <is>
-          <t>Diurnal</t>
+          <t>Cathemeral</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Antidorcas marsupialis</t>
+          <t>Lama glama</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Antidorcas marsupialis</t>
+          <t>Lama glama</t>
         </is>
       </c>
       <c r="C195">
@@ -13047,19 +13047,19 @@
       </c>
       <c r="Q195" t="inlineStr">
         <is>
-          <t>Cathemeral</t>
+          <t>Diurnal</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Tragelaphus strepsiceros</t>
+          <t>Antidorcas marsupialis</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Tragelaphus strepsiceros</t>
+          <t>Antidorcas marsupialis</t>
         </is>
       </c>
       <c r="C196">
@@ -13119,12 +13119,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Odocoileus virginianus</t>
+          <t>Tragelaphus strepsiceros</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Odocoileus virginianus</t>
+          <t>Tragelaphus strepsiceros</t>
         </is>
       </c>
       <c r="C197">
@@ -13152,10 +13152,10 @@
         <v>0</v>
       </c>
       <c r="K197">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L197">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="M197" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         </is>
       </c>
       <c r="N197">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -13177,19 +13177,19 @@
       </c>
       <c r="Q197" t="inlineStr">
         <is>
-          <t>Nocturnal</t>
+          <t>Cathemeral</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Giraffa camelopardalis</t>
+          <t>Odocoileus virginianus</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Giraffa camelopardalis</t>
+          <t>Odocoileus virginianus</t>
         </is>
       </c>
       <c r="C198">
@@ -13217,10 +13217,10 @@
         <v>0</v>
       </c>
       <c r="K198">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L198">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="N198">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -13249,63 +13249,128 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
+          <t>Giraffa camelopardalis</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Giraffa camelopardalis</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>0</v>
+      </c>
+      <c r="D199">
+        <v>0</v>
+      </c>
+      <c r="E199">
+        <v>0</v>
+      </c>
+      <c r="F199">
+        <v>0</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>0</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>100</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Other plant</t>
+        </is>
+      </c>
+      <c r="N199">
+        <v>1</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Herbivore</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Nocturnal</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
           <t>Balaenoptera acutorostrata</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>Balaenoptera acutorostrata</t>
         </is>
       </c>
-      <c r="C199">
+      <c r="C200">
         <v>70</v>
       </c>
-      <c r="D199">
-        <v>0</v>
-      </c>
-      <c r="E199">
-        <v>0</v>
-      </c>
-      <c r="F199">
+      <c r="D200">
+        <v>0</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
+      <c r="F200">
         <v>30</v>
       </c>
-      <c r="G199">
-        <v>0</v>
-      </c>
-      <c r="H199">
-        <v>0</v>
-      </c>
-      <c r="I199">
-        <v>0</v>
-      </c>
-      <c r="J199">
-        <v>0</v>
-      </c>
-      <c r="K199">
-        <v>0</v>
-      </c>
-      <c r="L199">
-        <v>0</v>
-      </c>
-      <c r="M199" t="inlineStr">
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>0</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+      <c r="M200" t="inlineStr">
         <is>
           <t>Invertebrates</t>
         </is>
       </c>
-      <c r="N199">
+      <c r="N200">
         <v>2</v>
       </c>
-      <c r="O199" t="inlineStr">
+      <c r="O200" t="inlineStr">
         <is>
           <t>Faunivore</t>
         </is>
       </c>
-      <c r="P199" t="inlineStr">
+      <c r="P200" t="inlineStr">
         <is>
           <t>Marine</t>
         </is>
       </c>
-      <c r="Q199" t="inlineStr">
+      <c r="Q200" t="inlineStr">
         <is>
           <t>Diurnal</t>
         </is>
@@ -13592,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACFCF95F-DB01-4958-9658-9F4031087C1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF10A43-CF85-4443-A687-BD6A181D52E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BE0DE4B-8D25-4E71-9BA3-610E9F6C2DC4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B75F3DB-E1DF-4091-B0B4-7E80A6380BA2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2331D628-6C09-4782-B394-F777428DD2C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E93B89E-9CB3-4926-B0CB-B9658B0A53CE}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BBF10A43-CF85-4443-A687-BD6A181D52E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BF3366C-9CE9-4D98-9499-4E246FEEF0F5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B75F3DB-E1DF-4091-B0B4-7E80A6380BA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8794DACA-DB74-4335-994C-C77EC2F6B4C8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E93B89E-9CB3-4926-B0CB-B9658B0A53CE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE890F49-AF9F-412F-8FF8-C90FFDAC592A}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BF3366C-9CE9-4D98-9499-4E246FEEF0F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AC5FAE3-0682-40D4-A377-EBFAAAD6C5E4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8794DACA-DB74-4335-994C-C77EC2F6B4C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42518ADE-A554-43D9-883E-0B68F45EB0F9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE890F49-AF9F-412F-8FF8-C90FFDAC592A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D257AD3-ABB4-41E5-A87D-97611DF64C7E}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AC5FAE3-0682-40D4-A377-EBFAAAD6C5E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C95A3BD-3FC7-48F6-83AE-596800B51B2F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42518ADE-A554-43D9-883E-0B68F45EB0F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D53FBDC-5C69-4A79-B508-208969AB5B15}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D257AD3-ABB4-41E5-A87D-97611DF64C7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68AAC7C5-443C-4D2E-A1BA-2DBC7B7938B0}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C95A3BD-3FC7-48F6-83AE-596800B51B2F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15554122-2F94-4441-9898-EFDF93D085D9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D53FBDC-5C69-4A79-B508-208969AB5B15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28AB6AEA-F94E-4820-B360-5873FF8E2433}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68AAC7C5-443C-4D2E-A1BA-2DBC7B7938B0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C85E8D4D-7941-4BF9-A89E-AF22BD083F6C}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15554122-2F94-4441-9898-EFDF93D085D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C887D11E-2B8F-43B0-AFCF-EA4FAA9FDC2E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28AB6AEA-F94E-4820-B360-5873FF8E2433}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813DD061-3FF1-4C6A-9A8C-888D8D92B0BB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C85E8D4D-7941-4BF9-A89E-AF22BD083F6C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FCD57C0-F6FC-46DD-B70D-7C7D2A66248B}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C887D11E-2B8F-43B0-AFCF-EA4FAA9FDC2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E36D7A3-A0D6-43CA-973E-C8D6D65197A3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{813DD061-3FF1-4C6A-9A8C-888D8D92B0BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D7190B1-9CF6-4F3B-B1B2-FC77C159A15D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FCD57C0-F6FC-46DD-B70D-7C7D2A66248B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22231B8-7BDB-484B-903F-2922ACCFF3D8}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E36D7A3-A0D6-43CA-973E-C8D6D65197A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92E58F6F-0F2C-4F7A-A55C-46258AEB4EF8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D7190B1-9CF6-4F3B-B1B2-FC77C159A15D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A3FF185-5F68-407F-B0A3-16FB5730BB80}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F22231B8-7BDB-484B-903F-2922ACCFF3D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{005FB831-CACB-43B9-914F-2634836DF530}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92E58F6F-0F2C-4F7A-A55C-46258AEB4EF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{106E6781-EC63-4AF0-A7DD-B33D1A14D823}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A3FF185-5F68-407F-B0A3-16FB5730BB80}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{652E6406-51E1-4FA1-8CFC-FEED1C9E3BE3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{005FB831-CACB-43B9-914F-2634836DF530}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9DF2FAE-B9B3-491D-845D-40D1CD2BDB32}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{106E6781-EC63-4AF0-A7DD-B33D1A14D823}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C64AB4A-0A7B-4F3E-A525-D880D507037A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{652E6406-51E1-4FA1-8CFC-FEED1C9E3BE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF93E79D-A7F6-4DD8-92D1-2C72C4EA7374}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9DF2FAE-B9B3-491D-845D-40D1CD2BDB32}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E893AEED-19D9-4450-84C0-BF52AB6A0933}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C64AB4A-0A7B-4F3E-A525-D880D507037A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81DA3059-1583-4279-A5D7-51D25D7C525F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF93E79D-A7F6-4DD8-92D1-2C72C4EA7374}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24374263-2746-4A35-87CA-34449449E7D4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E893AEED-19D9-4450-84C0-BF52AB6A0933}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4CB565C-3CE2-41C5-ACA8-A45AE725EB1D}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81DA3059-1583-4279-A5D7-51D25D7C525F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D12C46C-F729-499B-829B-ED676D7D315E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24374263-2746-4A35-87CA-34449449E7D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE4AD6A4-00A4-4653-9535-918E378C4D36}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4CB565C-3CE2-41C5-ACA8-A45AE725EB1D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03716C24-652A-4549-B26D-880A5D0F9446}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D12C46C-F729-499B-829B-ED676D7D315E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F5506E-C516-4909-B38D-4376ACD8061D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE4AD6A4-00A4-4653-9535-918E378C4D36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B180B2E-5738-4B90-ABA7-24B79D406AF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03716C24-652A-4549-B26D-880A5D0F9446}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D368B17-8B2A-4F7D-A3E9-6D9708B21C07}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7F5506E-C516-4909-B38D-4376ACD8061D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9EC0A59-52A9-48CE-8272-42BC8BC8F159}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B180B2E-5738-4B90-ABA7-24B79D406AF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E17EAE3A-B2FB-4D47-81CA-84063D1F045D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D368B17-8B2A-4F7D-A3E9-6D9708B21C07}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67203330-50F2-4898-B118-6F7C2EEA145D}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9EC0A59-52A9-48CE-8272-42BC8BC8F159}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55E63ED7-4A63-4057-A3D6-2E9F74EFA86D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E17EAE3A-B2FB-4D47-81CA-84063D1F045D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C898BFD7-65F8-4BAE-A311-E5B6D2329985}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67203330-50F2-4898-B118-6F7C2EEA145D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE1D204-907B-427B-9C61-1C809FA00294}"/>
 </file>
--- a/____EvoM1_TraitTable/diet_foraging.xlsx
+++ b/____EvoM1_TraitTable/diet_foraging.xlsx
@@ -13657,13 +13657,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55E63ED7-4A63-4057-A3D6-2E9F74EFA86D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7582D42-CF55-4BF5-94BB-8237596C4A6F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C898BFD7-65F8-4BAE-A311-E5B6D2329985}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A7E446F-B914-495F-95FF-7A126A4E48E9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFE1D204-907B-427B-9C61-1C809FA00294}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BE34745-1592-40F0-9D62-CDB1FF8D15D3}"/>
 </file>